--- a/data/trans_bre/POLIPATOLOGIA_5-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_5-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,17</t>
+          <t>-0,41; 3,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,59</t>
+          <t>3,22; 8,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 9,64</t>
+          <t>3,92; 9,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,75</t>
+          <t>2,43; 9,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 181,45</t>
+          <t>-16,79; 176,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,34; 299,32</t>
+          <t>59,35; 301,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,0; 303,57</t>
+          <t>64,82; 297,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,12; 117,88</t>
+          <t>21,22; 110,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,24</t>
+          <t>0,05; 4,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,71</t>
+          <t>3,44; 7,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,26</t>
+          <t>3,69; 8,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 13,49</t>
+          <t>6,66; 13,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 143,9</t>
+          <t>0,84; 154,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,57; 277,37</t>
+          <t>74,1; 285,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,27; 329,87</t>
+          <t>93,67; 343,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,04; 348,6</t>
+          <t>75,02; 346,13</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 9,49</t>
+          <t>4,16; 9,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,95</t>
+          <t>2,9; 8,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,66</t>
+          <t>2,8; 7,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 55,8</t>
+          <t>5,84; 59,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,75; 372,92</t>
+          <t>82,4; 371,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,41; 285,11</t>
+          <t>50,9; 268,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,18; 325,85</t>
+          <t>57,42; 308,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74,94; 925,06</t>
+          <t>72,56; 1135,76</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,51</t>
+          <t>1,46; 5,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,65</t>
+          <t>4,98; 9,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,58</t>
+          <t>4,82; 9,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 11,2</t>
+          <t>5,02; 11,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,79; 183,63</t>
+          <t>30,7; 183,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,63; 328,39</t>
+          <t>95,23; 351,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>107,23; 343,56</t>
+          <t>104,71; 376,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,4; 151,8</t>
+          <t>54,4; 155,57</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,48</t>
+          <t>2,34; 4,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,27</t>
+          <t>4,95; 7,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,58</t>
+          <t>5,17; 7,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 27,74</t>
+          <t>7,48; 27,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,86; 150,39</t>
+          <t>60,5; 149,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>110,47; 214,81</t>
+          <t>115,67; 227,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>127,29; 242,88</t>
+          <t>126,79; 243,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>86,67; 371,67</t>
+          <t>88,56; 365,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_5-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_5-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,54</t>
+          <t>7,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,22</t>
+          <t>-0,49; 3,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,75</t>
+          <t>3,0; 8,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,71</t>
+          <t>3,77; 9,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,69</t>
+          <t>4,79; 10,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 176,46</t>
+          <t>-19,82; 189,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,35; 301,47</t>
+          <t>59,02; 295,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,82; 297,61</t>
+          <t>70,2; 298,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 110,4</t>
+          <t>38,67; 120,67</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>141,11%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,13</t>
+          <t>0,47; 4,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,93</t>
+          <t>3,32; 7,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 8,14</t>
+          <t>3,53; 7,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,48</t>
+          <t>4,76; 9,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 154,59</t>
+          <t>9,31; 154,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,1; 285,43</t>
+          <t>71,85; 272,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,67; 343,6</t>
+          <t>84,79; 323,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,02; 346,13</t>
+          <t>49,94; 136,65</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,53</t>
+          <t>7,3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>340,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,32</t>
+          <t>3,97; 9,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,0</t>
+          <t>2,7; 7,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,64</t>
+          <t>2,85; 7,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 59,34</t>
+          <t>4,27; 9,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,4; 371,03</t>
+          <t>78,53; 384,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,9; 268,38</t>
+          <t>49,69; 273,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,42; 308,83</t>
+          <t>62,34; 320,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72,56; 1135,76</t>
+          <t>50,4; 173,57</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,52</t>
+          <t>9,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>100,45%</t>
+          <t>111,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,53</t>
+          <t>1,28; 5,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,91</t>
+          <t>5,0; 9,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 9,99</t>
+          <t>4,88; 9,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,72</t>
+          <t>6,72; 11,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,7; 183,58</t>
+          <t>26,8; 175,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,23; 351,97</t>
+          <t>96,52; 331,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>104,71; 376,71</t>
+          <t>105,58; 354,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,4; 155,57</t>
+          <t>71,21; 164,5</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,74</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>160,16%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,31</t>
+          <t>2,25; 4,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,34</t>
+          <t>4,83; 7,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,62</t>
+          <t>5,05; 7,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 27,48</t>
+          <t>6,67; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,5; 149,69</t>
+          <t>56,27; 145,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>115,67; 227,23</t>
+          <t>110,21; 221,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>126,79; 243,91</t>
+          <t>128,79; 250,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,56; 365,95</t>
+          <t>73,23; 120,11</t>
         </is>
       </c>
     </row>
